--- a/rtos-api-analysis/results/tizenrt_runtime_info.xlsx
+++ b/rtos-api-analysis/results/tizenrt_runtime_info.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>368</v>
+        <v>231</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -596,36 +596,37 @@
           <t>waitid</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B5" t="n">
+        <v>15367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>20235</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1627480</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: signal/sig_timedwait.c:190
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -676,7 +677,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -700,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -716,7 +717,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -756,21 +757,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -780,7 +781,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -836,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -875,36 +876,37 @@
           <t>pthread_cancel</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B12" t="n">
+        <v>23643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>38492</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1541101</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: group/group_leave.c:325
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -915,7 +917,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -955,7 +957,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -995,7 +997,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12631</v>
+        <v>8675</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1019,7 +1021,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1075,7 +1077,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1099,7 +1101,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1115,21 +1117,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1139,7 +1141,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1195,7 +1197,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1235,7 +1237,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1259,7 +1261,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1275,7 +1277,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1355,7 +1357,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1546</v>
+        <v>1391</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1379,7 +1381,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1395,7 +1397,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1419,7 +1421,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1435,7 +1437,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1475,7 +1477,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1515,7 +1517,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1595,7 +1597,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1662,7 +1664,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: group/group_leave.c:325
+          <t xml:space="preserve">KLEE: Execute: semaphore/sem_wait.c:122
 </t>
         </is>
       </c>
@@ -1714,7 +1716,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1738,7 +1740,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1833,7 +1835,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1857,7 +1859,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1873,7 +1875,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1913,7 +1915,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1953,7 +1955,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1993,7 +1995,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2073,7 +2075,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2097,7 +2099,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2113,7 +2115,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2272,7 +2274,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2339,7 +2341,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: wdog/wd_start.c:333
+          <t xml:space="preserve">KLEE: Execute: wdog/wd_start.c:368
 </t>
         </is>
       </c>
@@ -2391,7 +2393,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>517</v>
+        <v>460</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2415,7 +2417,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2431,7 +2433,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25893</v>
+        <v>16341</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2455,7 +2457,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2471,7 +2473,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2511,7 +2513,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2631,7 +2633,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2671,7 +2673,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2735,7 +2737,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2831,7 +2833,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2855,7 +2857,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2950,36 +2952,37 @@
           <t>pthread_kill</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B64" t="n">
+        <v>7294</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>15473</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>902082</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: mqueue/mq_waitirq.c:141
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2993,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3110,7 +3113,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3134,7 +3137,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3190,7 +3193,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3214,7 +3217,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3230,7 +3233,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3254,7 +3257,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3310,7 +3313,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3350,7 +3353,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3374,7 +3377,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3390,7 +3393,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3430,7 +3433,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3550,7 +3553,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3653,7 +3656,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3709,21 +3712,21 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3733,7 +3736,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3776,7 +3779,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: errno/errno_getptr.c:128
+          <t xml:space="preserve">KLEE: Execute: pthread/pthread_initialize.c:197
 </t>
         </is>
       </c>
@@ -3788,7 +3791,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3828,7 +3831,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3852,7 +3855,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3908,31 +3911,31 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1785</v>
+        <v>485</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>422</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>62363</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>257</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3948,7 +3951,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3988,7 +3991,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4068,7 +4071,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7851</v>
+        <v>4949</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4092,7 +4095,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4108,7 +4111,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6688</v>
+        <v>4930</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4132,7 +4135,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4148,7 +4151,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4172,7 +4175,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4188,7 +4191,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4228,7 +4231,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4387,7 +4390,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4411,7 +4414,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4427,7 +4430,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4451,7 +4454,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4466,36 +4469,37 @@
           <t>task_create</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B102" t="n">
+        <v>7701</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>14258</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>229549</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: sched/sched_free.c:135
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4625,11 +4629,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>511</v>
+        <v>84</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4644,7 +4648,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4745,7 +4749,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1358</v>
+        <v>822</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -4769,7 +4773,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4785,7 +4789,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>477</v>
+        <v>402</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4864,36 +4868,37 @@
           <t>task_delete</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B112" t="n">
+        <v>10446</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>14272</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>390922</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: group/group_leave.c:325
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4989,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5008,7 +5013,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5064,7 +5069,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5104,7 +5109,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>635</v>
+        <v>428</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5128,7 +5133,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5144,7 +5149,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5184,7 +5189,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5264,7 +5269,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5288,7 +5293,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5304,7 +5309,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -5328,7 +5333,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5344,7 +5349,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -5411,7 +5416,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: sched/sched_unlock.c:105
+          <t xml:space="preserve">KLEE: Execute: sched/sched_unlock.c:129
 </t>
         </is>
       </c>
@@ -5582,7 +5587,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -5662,7 +5667,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -5702,7 +5707,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -5726,7 +5731,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5742,7 +5747,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -5766,7 +5771,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5782,7 +5787,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -5806,7 +5811,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5822,7 +5827,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -5902,7 +5907,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -5942,7 +5947,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -5982,7 +5987,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6022,7 +6027,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6046,7 +6051,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6062,7 +6067,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -6181,7 +6186,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -6221,7 +6226,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -6245,7 +6250,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6261,7 +6266,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -6301,7 +6306,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -6421,7 +6426,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6525,7 +6530,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6541,7 +6546,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6581,7 +6586,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>15539</v>
+        <v>10322</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -6605,7 +6610,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6621,7 +6626,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -6660,36 +6665,37 @@
           <t>exit</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B157" t="n">
+        <v>6304</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>8148</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>127752</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: group/group_leave.c:325
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6746,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -6780,7 +6786,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1106</v>
+        <v>977</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -6804,7 +6810,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6844,7 +6850,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6900,7 +6906,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.8944099378881988</v>
+        <v>0.9316770186335404</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>

--- a/rtos-api-analysis/results/tizenrt_runtime_info.xlsx
+++ b/rtos-api-analysis/results/tizenrt_runtime_info.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -597,31 +597,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15367</v>
+        <v>14703</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1627480</t>
+          <t>1550506</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -876,37 +876,36 @@
           <t>pthread_cancel</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>23643</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>38492</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1541101</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35549</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t xml:space="preserve">KLEE: Execute: sched/sched_lock.c:113
+</t>
         </is>
       </c>
     </row>
@@ -917,7 +916,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -997,31 +996,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8675</v>
+        <v>8470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>761810</t>
+          <t>748804</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1077,31 +1076,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>184</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1117,7 +1116,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1157,7 +1156,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1237,7 +1236,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1357,7 +1356,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1391</v>
+        <v>1339</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1366,22 +1365,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>92200</t>
+          <t>90190</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1437,7 +1436,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1477,7 +1476,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1557,7 +1556,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1636,36 +1635,37 @@
           <t>task_restart</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3565</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>242844</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: semaphore/sem_wait.c:122
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2433,31 +2433,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>16341</v>
+        <v>15602</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1618964</t>
+          <t>1542502</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2953,31 +2953,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7294</v>
+        <v>7252</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>902082</t>
+          <t>877012</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3193,31 +3193,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3362,22 +3362,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>723</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: pthread/pthread_initialize.c:197
+          <t xml:space="preserve">KLEE: Execute: errno/errno_getptr.c:109
 </t>
         </is>
       </c>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4949</v>
+        <v>5481</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4080,22 +4080,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>523352</t>
+          <t>521342</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4930</v>
+        <v>5108</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4120,22 +4120,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>395512</t>
+          <t>393502</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4160,22 +4160,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>707</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>7701</v>
+        <v>7887</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4479,22 +4479,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>229549</t>
+          <t>227539</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>822</v>
+        <v>898</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -4869,31 +4869,31 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>10446</v>
+        <v>13908</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>390922</t>
+          <t>693623</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5069,31 +5069,31 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>246</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5109,31 +5109,31 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>535</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>423</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -5388,36 +5388,37 @@
           <t>mq_send</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B125" t="n">
+        <v>27428</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>50544</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3099081</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: sched/sched_unlock.c:129
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5588,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -5667,7 +5668,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -5707,7 +5708,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -5747,7 +5748,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -5787,7 +5788,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -5796,22 +5797,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5987,7 +5988,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6027,7 +6028,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6226,7 +6227,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -6426,7 +6427,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -6466,7 +6467,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -6506,7 +6507,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6546,7 +6547,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6586,31 +6587,31 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>10322</v>
+        <v>8858</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>918478</t>
+          <t>769952</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6666,31 +6667,31 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>6304</v>
+        <v>6292</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>127752</t>
+          <t>122812</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6746,7 +6747,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -6786,7 +6787,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -6826,7 +6827,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -6906,7 +6907,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.9316770186335404</v>
+        <v>0.937888198757764</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
